--- a/数据表/Entity/Entity.xlsx
+++ b/数据表/Entity/Entity.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
   <si>
     <t>#</t>
   </si>
@@ -56,6 +56,12 @@
     <t>资源名称</t>
   </si>
   <si>
+    <t>跟随相机</t>
+  </si>
+  <si>
+    <t>FollowCamera</t>
+  </si>
+  <si>
     <t>测试玩家</t>
   </si>
   <si>
@@ -74,12 +80,6 @@
     <t>RemoteEnemy</t>
   </si>
   <si>
-    <t>跟随相机</t>
-  </si>
-  <si>
-    <t>FollowCamera</t>
-  </si>
-  <si>
     <t>武器小刀</t>
   </si>
   <si>
@@ -96,6 +96,12 @@
   </si>
   <si>
     <t>WeaponSlash</t>
+  </si>
+  <si>
+    <t>武器闪电</t>
+  </si>
+  <si>
+    <t>WeaponLightning</t>
   </si>
   <si>
     <t>金币实体</t>
@@ -1255,7 +1261,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="8.72727272727273" style="1"/>
@@ -1310,7 +1316,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="B5" s="1">
-        <v>1001</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>9</v>
@@ -1321,7 +1327,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="1">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>11</v>
@@ -1332,7 +1338,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="B7" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>13</v>
@@ -1343,7 +1349,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1">
-        <v>11</v>
+        <v>102</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>15</v>
@@ -1387,7 +1393,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="B12" s="1">
-        <v>10001</v>
+        <v>204</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>23</v>
@@ -1398,13 +1404,24 @@
     </row>
     <row r="13" spans="1:4">
       <c r="B13" s="1">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="B14" s="1">
+        <v>10002</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/数据表/Entity/Entity.xlsx
+++ b/数据表/Entity/Entity.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="21550" windowHeight="10080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>#</t>
   </si>
@@ -102,6 +102,12 @@
   </si>
   <si>
     <t>WeaponLightning</t>
+  </si>
+  <si>
+    <t>武器长枪</t>
+  </si>
+  <si>
+    <t>WeaponLance</t>
   </si>
   <si>
     <t>金币实体</t>
@@ -1261,7 +1267,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="8.72727272727273" style="1"/>
@@ -1404,7 +1410,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="B13" s="1">
-        <v>10001</v>
+        <v>205</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>25</v>
@@ -1415,13 +1421,24 @@
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="1">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="B15" s="1">
+        <v>10002</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
